--- a/public/exports-with-coowners/29189846.xlsx
+++ b/public/exports-with-coowners/29189846.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311279891</t>
+          <t xml:space="preserve">311279903</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311279890</t>
+          <t xml:space="preserve">311279903</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -8314,7 +8314,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311282669</t>
+          <t xml:space="preserve">311372348</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -19714,12 +19714,12 @@
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t xml:space="preserve">311369509</t>
+          <t xml:space="preserve">311374076</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M263" t="inlineStr">
@@ -22339,12 +22339,12 @@
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290661</t>
+          <t xml:space="preserve">311290663</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M298" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290666</t>
+          <t xml:space="preserve">311374773</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
@@ -24364,12 +24364,12 @@
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291095</t>
+          <t xml:space="preserve">311373742</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M325" t="inlineStr">
@@ -24814,12 +24814,12 @@
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293774</t>
+          <t xml:space="preserve">311373757</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M331" t="inlineStr">
@@ -25039,7 +25039,7 @@
       </c>
       <c r="K334" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293846</t>
+          <t xml:space="preserve">311293847</t>
         </is>
       </c>
       <c r="L334" t="inlineStr">

--- a/public/exports-with-coowners/29189846.xlsx
+++ b/public/exports-with-coowners/29189846.xlsx
@@ -7264,12 +7264,12 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311279903</t>
+          <t xml:space="preserve">311279891</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311279903</t>
+          <t xml:space="preserve">311279890</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -8314,7 +8314,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372348</t>
+          <t xml:space="preserve">311282669</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -19714,12 +19714,12 @@
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374076</t>
+          <t xml:space="preserve">311369509</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
@@ -22339,12 +22339,12 @@
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290663</t>
+          <t xml:space="preserve">311290661</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374773</t>
+          <t xml:space="preserve">311290666</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
@@ -22466,7 +22466,7 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stænderpladsen 2</t>
+          <t xml:space="preserve">Tapdrupvej 100</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
@@ -22476,20 +22476,20 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t xml:space="preserve">9431029</t>
+          <t xml:space="preserve">3454867</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J300">
-        <v>1500</v>
+        <v>488</v>
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t xml:space="preserve">311368829</t>
+          <t xml:space="preserve">311375102</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
@@ -22556,15 +22556,15 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J301">
-        <v>488</v>
+        <v>284</v>
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375102</t>
+          <t xml:space="preserve">311375108</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
@@ -22616,7 +22616,7 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tapdrupvej 100</t>
+          <t xml:space="preserve">Tapdrupvej 100A</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
@@ -22631,15 +22631,15 @@
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J302">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375108</t>
+          <t xml:space="preserve">311368613</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
@@ -22691,7 +22691,7 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tapdrupvej 100A</t>
+          <t xml:space="preserve">Tingvej 17</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
@@ -22701,20 +22701,20 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t xml:space="preserve">3454867</t>
+          <t xml:space="preserve">5589413</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="J303">
-        <v>273</v>
+        <v>1281</v>
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t xml:space="preserve">311368613</t>
+          <t xml:space="preserve">311375539</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
@@ -22766,7 +22766,7 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingvej 17</t>
+          <t xml:space="preserve">Tingvej 5</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
@@ -22776,20 +22776,20 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t xml:space="preserve">5589413</t>
+          <t xml:space="preserve">5591355</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J304">
-        <v>1281</v>
+        <v>3916</v>
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375539</t>
+          <t xml:space="preserve">311375512</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
@@ -22841,7 +22841,7 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingvej 5</t>
+          <t xml:space="preserve">Vinkelvej 172</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
@@ -22851,20 +22851,20 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t xml:space="preserve">5591355</t>
+          <t xml:space="preserve">4012634</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J305">
-        <v>3916</v>
+        <v>387</v>
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375512</t>
+          <t xml:space="preserve">311375598</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
@@ -22916,7 +22916,7 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vinkelvej 172</t>
+          <t xml:space="preserve">Vinkelvej 18A</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
@@ -22926,7 +22926,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t xml:space="preserve">4012634</t>
+          <t xml:space="preserve">8838279</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -22935,11 +22935,11 @@
         </is>
       </c>
       <c r="J306">
-        <v>387</v>
+        <v>284</v>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375598</t>
+          <t xml:space="preserve">311290692</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
@@ -22991,17 +22991,17 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vinkelvej 18A</t>
+          <t xml:space="preserve">Vorningvej 33</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">8830</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t xml:space="preserve">8838279</t>
+          <t xml:space="preserve">3468562</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -23010,11 +23010,11 @@
         </is>
       </c>
       <c r="J307">
-        <v>284</v>
+        <v>5165</v>
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290692</t>
+          <t xml:space="preserve">311375628</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
@@ -23066,7 +23066,7 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vorningvej 33</t>
+          <t xml:space="preserve">Vorningvej 33A</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
@@ -23081,15 +23081,15 @@
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J308">
-        <v>5165</v>
+        <v>813</v>
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375628</t>
+          <t xml:space="preserve">311290695</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
@@ -23141,30 +23141,30 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vorningvej 33A</t>
+          <t xml:space="preserve">Ådalshøjen 2</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t xml:space="preserve">8830</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t xml:space="preserve">3468562</t>
+          <t xml:space="preserve">8074164</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J309">
-        <v>813</v>
+        <v>722</v>
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290695</t>
+          <t xml:space="preserve">311375648</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
@@ -23216,17 +23216,17 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ådalshøjen 2</t>
+          <t xml:space="preserve">Skolen 3</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">7470</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t xml:space="preserve">8074164</t>
+          <t xml:space="preserve">9214926</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -23235,11 +23235,11 @@
         </is>
       </c>
       <c r="J310">
-        <v>722</v>
+        <v>2661</v>
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375648</t>
+          <t xml:space="preserve">311372723</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
@@ -23249,7 +23249,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-28</t>
+          <t xml:space="preserve">2027-12-29</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -23306,11 +23306,11 @@
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J311">
-        <v>2661</v>
+        <v>1945</v>
       </c>
       <c r="K311" t="inlineStr">
         <is>
@@ -23381,11 +23381,11 @@
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J312">
-        <v>1945</v>
+        <v>422</v>
       </c>
       <c r="K312" t="inlineStr">
         <is>
@@ -23456,11 +23456,11 @@
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J313">
-        <v>422</v>
+        <v>1025</v>
       </c>
       <c r="K313" t="inlineStr">
         <is>
@@ -23531,11 +23531,11 @@
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J314">
-        <v>1025</v>
+        <v>898</v>
       </c>
       <c r="K314" t="inlineStr">
         <is>
@@ -23591,30 +23591,30 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolen 3</t>
+          <t xml:space="preserve">Egeskovvej 75</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t xml:space="preserve">7470</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t xml:space="preserve">9214926</t>
+          <t xml:space="preserve">3451289</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J315">
-        <v>898</v>
+        <v>1067</v>
       </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372723</t>
+          <t xml:space="preserve">311290810</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
@@ -23624,7 +23624,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-29</t>
+          <t xml:space="preserve">2027-12-30</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -23681,11 +23681,11 @@
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J316">
-        <v>1067</v>
+        <v>444</v>
       </c>
       <c r="K316" t="inlineStr">
         <is>
@@ -23756,11 +23756,11 @@
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="J317">
-        <v>444</v>
+        <v>976</v>
       </c>
       <c r="K317" t="inlineStr">
         <is>
@@ -23831,11 +23831,11 @@
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J318">
-        <v>976</v>
+        <v>1673</v>
       </c>
       <c r="K318" t="inlineStr">
         <is>
@@ -23906,11 +23906,11 @@
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J319">
-        <v>1673</v>
+        <v>3803</v>
       </c>
       <c r="K319" t="inlineStr">
         <is>
@@ -23981,11 +23981,11 @@
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J320">
-        <v>3803</v>
+        <v>380</v>
       </c>
       <c r="K320" t="inlineStr">
         <is>
@@ -24056,15 +24056,15 @@
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J321">
-        <v>380</v>
+        <v>306</v>
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290810</t>
+          <t xml:space="preserve">311290811</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
@@ -24116,7 +24116,7 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egeskovvej 75</t>
+          <t xml:space="preserve">Egeskovvej 4</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
@@ -24126,20 +24126,20 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t xml:space="preserve">3451289</t>
+          <t xml:space="preserve">8371196</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="J322">
-        <v>306</v>
+        <v>275</v>
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290811</t>
+          <t xml:space="preserve">311291090</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
@@ -24149,7 +24149,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-30</t>
+          <t xml:space="preserve">2028-01-04</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -24191,35 +24191,35 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egeskovvej 4</t>
+          <t xml:space="preserve">Gl. Banevej 8</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">7470</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t xml:space="preserve">8371196</t>
+          <t xml:space="preserve">379840, 379841</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J323">
-        <v>275</v>
+        <v>3301</v>
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291090</t>
+          <t xml:space="preserve">311291149</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M323" t="inlineStr">
@@ -24266,17 +24266,17 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl. Banevej 8</t>
+          <t xml:space="preserve">Kærsangervej 252</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t xml:space="preserve">7470</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t xml:space="preserve">379840, 379841</t>
+          <t xml:space="preserve">7715426</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -24285,11 +24285,11 @@
         </is>
       </c>
       <c r="J324">
-        <v>3301</v>
+        <v>635</v>
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291149</t>
+          <t xml:space="preserve">311291095</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
@@ -24341,7 +24341,7 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærsangervej 252</t>
+          <t xml:space="preserve">Safranvej 10A</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
@@ -24351,20 +24351,20 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t xml:space="preserve">7715426</t>
+          <t xml:space="preserve">9254134</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J325">
-        <v>635</v>
+        <v>267</v>
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373742</t>
+          <t xml:space="preserve">311291091</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
@@ -24416,7 +24416,7 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t xml:space="preserve">Safranvej 10A</t>
+          <t xml:space="preserve">Sct. Laurentii Vej 14C</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
@@ -24426,25 +24426,25 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t xml:space="preserve">9254134</t>
+          <t xml:space="preserve">5591308</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J326">
-        <v>267</v>
+        <v>384</v>
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291091</t>
+          <t xml:space="preserve">311372532</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M326" t="inlineStr">
@@ -24491,35 +24491,35 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sct. Laurentii Vej 14C</t>
+          <t xml:space="preserve">Tjele Møllevej 10</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">8830</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t xml:space="preserve">5591308</t>
+          <t xml:space="preserve">3455227</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J327">
-        <v>384</v>
+        <v>2628</v>
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372532</t>
+          <t xml:space="preserve">311291101</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M327" t="inlineStr">
@@ -24566,17 +24566,17 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjele Møllevej 10</t>
+          <t xml:space="preserve">Guldblommevej 14</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t xml:space="preserve">8830</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t xml:space="preserve">3455227</t>
+          <t xml:space="preserve">5587531</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -24585,11 +24585,11 @@
         </is>
       </c>
       <c r="J328">
-        <v>2628</v>
+        <v>836</v>
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291101</t>
+          <t xml:space="preserve">311293801</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
@@ -24599,7 +24599,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-04</t>
+          <t xml:space="preserve">2028-01-22</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -24641,7 +24641,7 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guldblommevej 14</t>
+          <t xml:space="preserve">Guldblommevej 16</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
@@ -24656,7 +24656,7 @@
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J329">
@@ -24664,7 +24664,7 @@
       </c>
       <c r="K329" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293801</t>
+          <t xml:space="preserve">311293850</t>
         </is>
       </c>
       <c r="L329" t="inlineStr">
@@ -24716,7 +24716,7 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guldblommevej 16</t>
+          <t xml:space="preserve">Liseborg Hegn 10A</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
@@ -24726,25 +24726,25 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t xml:space="preserve">5587531</t>
+          <t xml:space="preserve">10227103</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J330">
-        <v>836</v>
+        <v>6616</v>
       </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293850</t>
+          <t xml:space="preserve">311293774</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M330" t="inlineStr">
@@ -24791,7 +24791,7 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liseborg Hegn 10A</t>
+          <t xml:space="preserve">Ll. Sct. Hans Gade 7</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
@@ -24801,20 +24801,20 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t xml:space="preserve">10227103</t>
+          <t xml:space="preserve">100002554</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J331">
-        <v>6616</v>
+        <v>464</v>
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373757</t>
+          <t xml:space="preserve">311373762</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
@@ -24866,7 +24866,7 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ll. Sct. Hans Gade 7</t>
+          <t xml:space="preserve">Ll. Sct. Hans Gade 9</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
@@ -24881,11 +24881,11 @@
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J332">
-        <v>464</v>
+        <v>1037</v>
       </c>
       <c r="K332" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ll. Sct. Hans Gade 9</t>
+          <t xml:space="preserve">Merkurvej 71</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
@@ -24951,7 +24951,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t xml:space="preserve">100002554</t>
+          <t xml:space="preserve">3449917</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -24960,11 +24960,11 @@
         </is>
       </c>
       <c r="J333">
-        <v>1037</v>
+        <v>594</v>
       </c>
       <c r="K333" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373762</t>
+          <t xml:space="preserve">311293846</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
@@ -25016,7 +25016,7 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t xml:space="preserve">Merkurvej 71</t>
+          <t xml:space="preserve">Rødevej 2A</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
@@ -25026,7 +25026,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t xml:space="preserve">3449917</t>
+          <t xml:space="preserve">8940099</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -25035,11 +25035,11 @@
         </is>
       </c>
       <c r="J334">
-        <v>594</v>
+        <v>1569</v>
       </c>
       <c r="K334" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293847</t>
+          <t xml:space="preserve">311374142</t>
         </is>
       </c>
       <c r="L334" t="inlineStr">
@@ -25091,17 +25091,17 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rødevej 2A</t>
+          <t xml:space="preserve">Skolegade 27</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">9632</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t xml:space="preserve">8940099</t>
+          <t xml:space="preserve">3464052</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -25110,11 +25110,11 @@
         </is>
       </c>
       <c r="J335">
-        <v>1569</v>
+        <v>2918</v>
       </c>
       <c r="K335" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374142</t>
+          <t xml:space="preserve">311372613</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
@@ -25181,15 +25181,15 @@
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J336">
-        <v>2918</v>
+        <v>294</v>
       </c>
       <c r="K336" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372613</t>
+          <t xml:space="preserve">311374196</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
@@ -25256,15 +25256,15 @@
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J337">
-        <v>294</v>
+        <v>2275</v>
       </c>
       <c r="K337" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374196</t>
+          <t xml:space="preserve">311293831</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
@@ -25331,15 +25331,15 @@
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J338">
-        <v>2275</v>
+        <v>333</v>
       </c>
       <c r="K338" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293831</t>
+          <t xml:space="preserve">311293833</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
@@ -25391,7 +25391,7 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 27</t>
+          <t xml:space="preserve">Skolegade 29</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
@@ -25406,15 +25406,15 @@
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J339">
-        <v>333</v>
+        <v>297</v>
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293833</t>
+          <t xml:space="preserve">311374191</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
@@ -25451,12 +25451,12 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t xml:space="preserve">Viborg Kommune</t>
+          <t xml:space="preserve">Boligselskabet Sct. Jørgen, Viborg</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -25466,30 +25466,30 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 29</t>
+          <t xml:space="preserve">Videbechs Alle 165A</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t xml:space="preserve">9632</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t xml:space="preserve">3464052</t>
+          <t xml:space="preserve">383686, 383688, 383687, 383689</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">29</t>
         </is>
       </c>
       <c r="J340">
-        <v>297</v>
+        <v>734</v>
       </c>
       <c r="K340" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374191</t>
+          <t xml:space="preserve">311375579</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
@@ -25526,12 +25526,12 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boligselskabet Sct. Jørgen, Viborg</t>
+          <t xml:space="preserve">Viborg Kommune</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -25541,7 +25541,7 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t xml:space="preserve">Videbechs Alle 165A</t>
+          <t xml:space="preserve">Liseborgvej 35A</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
@@ -25551,30 +25551,30 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t xml:space="preserve">383686, 383688, 383687, 383689</t>
+          <t xml:space="preserve">1508276, 100535682</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t xml:space="preserve">29</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J341">
-        <v>734</v>
+        <v>854</v>
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375579</t>
+          <t xml:space="preserve">311373759</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-22</t>
+          <t xml:space="preserve">2028-02-15</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -25616,40 +25616,40 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liseborgvej 35A</t>
+          <t xml:space="preserve">Brandstrupvej 27</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">8840</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t xml:space="preserve">1508276, 100535682</t>
+          <t xml:space="preserve">4011561</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J342">
-        <v>854</v>
+        <v>1178</v>
       </c>
       <c r="K342" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373759</t>
+          <t xml:space="preserve">311369993</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Dansk Energisyn</t>
         </is>
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-15</t>
+          <t xml:space="preserve">2029-04-09</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -25676,12 +25676,12 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t xml:space="preserve">Viborg Kommune</t>
+          <t xml:space="preserve">Mercantec</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -25691,40 +25691,40 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brandstrupvej 27</t>
+          <t xml:space="preserve">Banegårds Alle 1</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t xml:space="preserve">8840</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t xml:space="preserve">4011561</t>
+          <t xml:space="preserve">430971, 430972</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J343">
-        <v>1178</v>
+        <v>15028</v>
       </c>
       <c r="K343" t="inlineStr">
         <is>
-          <t xml:space="preserve">311369993</t>
+          <t xml:space="preserve">311431225</t>
         </is>
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Energisyn</t>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-04-09</t>
+          <t xml:space="preserve">2030-04-01</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -25751,12 +25751,12 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercantec</t>
+          <t xml:space="preserve">Viborg Kommune</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -25766,40 +25766,40 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t xml:space="preserve">Banegårds Alle 1</t>
+          <t xml:space="preserve">Stadionvej 6A</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">8832</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t xml:space="preserve">430971, 430972</t>
+          <t xml:space="preserve">3464853</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J344">
-        <v>15028</v>
+        <v>335</v>
       </c>
       <c r="K344" t="inlineStr">
         <is>
-          <t xml:space="preserve">311431225</t>
+          <t xml:space="preserve">311467972</t>
         </is>
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
         </is>
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-04-01</t>
+          <t xml:space="preserve">2030-10-19</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -25826,12 +25826,12 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t xml:space="preserve">Viborg Kommune</t>
+          <t xml:space="preserve">ABF Torvegadecentret</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -25841,40 +25841,40 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 6A</t>
+          <t xml:space="preserve">Torvegade 10A</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t xml:space="preserve">8832</t>
+          <t xml:space="preserve">8850</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t xml:space="preserve">3464853</t>
+          <t xml:space="preserve">379369, 379370, 379371, 379372, 379373, 379374</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J345">
-        <v>335</v>
+        <v>3439</v>
       </c>
       <c r="K345" t="inlineStr">
         <is>
-          <t xml:space="preserve">311467972</t>
+          <t xml:space="preserve">311474838</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-19</t>
+          <t xml:space="preserve">2030-11-11</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -25901,12 +25901,12 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t xml:space="preserve">ABF Torvegadecentret</t>
+          <t xml:space="preserve">Viborg Kommune</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -25916,40 +25916,40 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvegade 10A</t>
+          <t xml:space="preserve">Rørsangervej 5</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t xml:space="preserve">8850</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t xml:space="preserve">379369, 379370, 379371, 379372, 379373, 379374</t>
+          <t xml:space="preserve">5586340</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J346">
-        <v>3439</v>
+        <v>313</v>
       </c>
       <c r="K346" t="inlineStr">
         <is>
-          <t xml:space="preserve">311474838</t>
+          <t xml:space="preserve">311476458</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">Ydes Bygningsrådgivning</t>
         </is>
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-11</t>
+          <t xml:space="preserve">2030-11-17</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -25991,7 +25991,7 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rørsangervej 5</t>
+          <t xml:space="preserve">Søakset 2</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
@@ -26001,30 +26001,30 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t xml:space="preserve">5586340</t>
+          <t xml:space="preserve">100124844</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J347">
-        <v>313</v>
+        <v>1565</v>
       </c>
       <c r="K347" t="inlineStr">
         <is>
-          <t xml:space="preserve">311476458</t>
+          <t xml:space="preserve">311505527</t>
         </is>
       </c>
       <c r="L347" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ydes Bygningsrådgivning</t>
+          <t xml:space="preserve">Trykprøvning &amp; Energimærkning Danmark ApS</t>
         </is>
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-17</t>
+          <t xml:space="preserve">2031-03-22</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -26066,40 +26066,40 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søakset 2</t>
+          <t xml:space="preserve">Naundrupvej 7A</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">9632</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t xml:space="preserve">100124844</t>
+          <t xml:space="preserve">749066, 3456742</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J348">
-        <v>1565</v>
+        <v>348</v>
       </c>
       <c r="K348" t="inlineStr">
         <is>
-          <t xml:space="preserve">311505527</t>
+          <t xml:space="preserve">311540479</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trykprøvning &amp; Energimærkning Danmark ApS</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-22</t>
+          <t xml:space="preserve">2031-08-12</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -26126,12 +26126,12 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t xml:space="preserve">Viborg Kommune</t>
+          <t xml:space="preserve">Boligselskabet Sct. Jørgen, Viborg</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -26141,40 +26141,40 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naundrupvej 7A</t>
+          <t xml:space="preserve">Marsk Stigs Vej 4</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t xml:space="preserve">9632</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t xml:space="preserve">749066, 3456742</t>
+          <t xml:space="preserve">421278, 421279, 421280</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J349">
-        <v>348</v>
+        <v>9880</v>
       </c>
       <c r="K349" t="inlineStr">
         <is>
-          <t xml:space="preserve">311540479</t>
+          <t xml:space="preserve">311599601</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">Sweco Danmark A/S - LBF</t>
         </is>
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-12</t>
+          <t xml:space="preserve">2032-05-11</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -26201,12 +26201,12 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boligselskabet Sct. Jørgen, Viborg</t>
+          <t xml:space="preserve">Viborg Kommune</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -26216,30 +26216,30 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marsk Stigs Vej 4</t>
+          <t xml:space="preserve">Anlægsgade 2</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">7850</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t xml:space="preserve">421278, 421279, 421280</t>
+          <t xml:space="preserve">384187, 384188</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J350">
-        <v>9880</v>
+        <v>3245</v>
       </c>
       <c r="K350" t="inlineStr">
         <is>
-          <t xml:space="preserve">311599601</t>
+          <t xml:space="preserve">311619862</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
@@ -26249,7 +26249,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-11</t>
+          <t xml:space="preserve">2032-08-11</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -26276,12 +26276,12 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t xml:space="preserve">Viborg Kommune</t>
+          <t xml:space="preserve">Professionshøjskolen VIA University College</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -26291,17 +26291,17 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anlægsgade 2</t>
+          <t xml:space="preserve">Prinsens Alle 2</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t xml:space="preserve">7850</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t xml:space="preserve">384187, 384188</t>
+          <t xml:space="preserve">382460, 382461</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -26310,21 +26310,21 @@
         </is>
       </c>
       <c r="J351">
-        <v>3245</v>
+        <v>20359</v>
       </c>
       <c r="K351" t="inlineStr">
         <is>
-          <t xml:space="preserve">311619862</t>
+          <t xml:space="preserve">311622987</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S - LBF</t>
+          <t xml:space="preserve">Norconsult A/S</t>
         </is>
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-11</t>
+          <t xml:space="preserve">2032-08-25</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -26351,12 +26351,12 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t xml:space="preserve">Professionshøjskolen VIA University College</t>
+          <t xml:space="preserve">Viborg Kommune</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -26366,7 +26366,7 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prinsens Alle 2</t>
+          <t xml:space="preserve">Tingvej 20</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
@@ -26376,7 +26376,7 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t xml:space="preserve">382460, 382461</t>
+          <t xml:space="preserve">5589417</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -26385,11 +26385,11 @@
         </is>
       </c>
       <c r="J352">
-        <v>20359</v>
+        <v>8141</v>
       </c>
       <c r="K352" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622987</t>
+          <t xml:space="preserve">311652390</t>
         </is>
       </c>
       <c r="L352" t="inlineStr">
@@ -26399,7 +26399,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-25</t>
+          <t xml:space="preserve">2033-01-04</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -26441,7 +26441,7 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingvej 20</t>
+          <t xml:space="preserve">H.C. Andersens Vej 5</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
@@ -26451,30 +26451,30 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t xml:space="preserve">5589417</t>
+          <t xml:space="preserve">5590613</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J353">
-        <v>8141</v>
+        <v>478</v>
       </c>
       <c r="K353" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652390</t>
+          <t xml:space="preserve">311659256</t>
         </is>
       </c>
       <c r="L353" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norconsult A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-04</t>
+          <t xml:space="preserve">2033-02-09</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -26516,7 +26516,7 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t xml:space="preserve">H.C. Andersens Vej 5</t>
+          <t xml:space="preserve">Rørsangervej 5</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
@@ -26526,30 +26526,30 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t xml:space="preserve">5590613</t>
+          <t xml:space="preserve">5586340</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J354">
-        <v>478</v>
+        <v>357</v>
       </c>
       <c r="K354" t="inlineStr">
         <is>
-          <t xml:space="preserve">311659256</t>
+          <t xml:space="preserve">311661783</t>
         </is>
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Tæthedskompagniet ApS</t>
         </is>
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-09</t>
+          <t xml:space="preserve">2033-02-22</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -26576,12 +26576,12 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t xml:space="preserve">Viborg Kommune</t>
+          <t xml:space="preserve">Boligselskabet Sct. Jørgen, Viborg</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -26591,7 +26591,7 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rørsangervej 5</t>
+          <t xml:space="preserve">Blichersvænge 1</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
@@ -26601,30 +26601,30 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t xml:space="preserve">5586340</t>
+          <t xml:space="preserve">100178735, 100178736</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J355">
-        <v>357</v>
+        <v>872</v>
       </c>
       <c r="K355" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661783</t>
+          <t xml:space="preserve">311685873</t>
         </is>
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tæthedskompagniet ApS</t>
+          <t xml:space="preserve">Sweco Danmark A/S - LBF</t>
         </is>
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-22</t>
+          <t xml:space="preserve">2033-06-06</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -26666,30 +26666,30 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blichersvænge 1</t>
+          <t xml:space="preserve">Nørregade 3</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">8830</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t xml:space="preserve">100178735, 100178736</t>
+          <t xml:space="preserve">384199, 384200</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J356">
-        <v>872</v>
+        <v>2115</v>
       </c>
       <c r="K356" t="inlineStr">
         <is>
-          <t xml:space="preserve">311685873</t>
+          <t xml:space="preserve">311685866</t>
         </is>
       </c>
       <c r="L356" t="inlineStr">
@@ -26726,12 +26726,12 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boligselskabet Sct. Jørgen, Viborg</t>
+          <t xml:space="preserve">Viborg Kommune</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -26741,17 +26741,17 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 3</t>
+          <t xml:space="preserve">Banegårdspladsen 4</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t xml:space="preserve">8830</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t xml:space="preserve">384199, 384200</t>
+          <t xml:space="preserve">381021, 381022, 381023, 381024, 381025</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -26760,11 +26760,11 @@
         </is>
       </c>
       <c r="J357">
-        <v>2115</v>
+        <v>1814</v>
       </c>
       <c r="K357" t="inlineStr">
         <is>
-          <t xml:space="preserve">311685866</t>
+          <t xml:space="preserve">311702960</t>
         </is>
       </c>
       <c r="L357" t="inlineStr">
@@ -26774,7 +26774,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-06</t>
+          <t xml:space="preserve">2033-08-27</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -26801,12 +26801,12 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t xml:space="preserve">Viborg Kommune</t>
+          <t xml:space="preserve">BOLIGSELSKABET VIBORG</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -26816,7 +26816,7 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t xml:space="preserve">Banegårdspladsen 4</t>
+          <t xml:space="preserve">N.F.S. Grundtvigs Vej 13</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
@@ -26826,7 +26826,7 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t xml:space="preserve">381021, 381022, 381023, 381024, 381025</t>
+          <t xml:space="preserve">384785, 384786, 384787</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -26835,11 +26835,11 @@
         </is>
       </c>
       <c r="J358">
-        <v>1814</v>
+        <v>10635</v>
       </c>
       <c r="K358" t="inlineStr">
         <is>
-          <t xml:space="preserve">311702960</t>
+          <t xml:space="preserve">311757301</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">
@@ -26849,7 +26849,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-27</t>
+          <t xml:space="preserve">2034-05-06</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -26891,7 +26891,7 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t xml:space="preserve">N.F.S. Grundtvigs Vej 13</t>
+          <t xml:space="preserve">Odshøjvej 5A</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
@@ -26901,7 +26901,7 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t xml:space="preserve">384785, 384786, 384787</t>
+          <t xml:space="preserve">383742, 383743, 383744</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -26910,11 +26910,11 @@
         </is>
       </c>
       <c r="J359">
-        <v>10635</v>
+        <v>1930</v>
       </c>
       <c r="K359" t="inlineStr">
         <is>
-          <t xml:space="preserve">311757301</t>
+          <t xml:space="preserve">311757916</t>
         </is>
       </c>
       <c r="L359" t="inlineStr">
@@ -26924,7 +26924,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-05-06</t>
+          <t xml:space="preserve">2034-05-08</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -26951,12 +26951,12 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOLIGSELSKABET VIBORG</t>
+          <t xml:space="preserve">Viborg Kommune</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -26966,40 +26966,40 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t xml:space="preserve">Odshøjvej 5A</t>
+          <t xml:space="preserve">Jørgens Alle 42</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">8850</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t xml:space="preserve">383742, 383743, 383744</t>
+          <t xml:space="preserve">7775696</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J360">
-        <v>1930</v>
+        <v>394</v>
       </c>
       <c r="K360" t="inlineStr">
         <is>
-          <t xml:space="preserve">311757916</t>
+          <t xml:space="preserve">311764588</t>
         </is>
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S - LBF</t>
+          <t xml:space="preserve">Ydes Bygningsrådgivning</t>
         </is>
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-05-08</t>
+          <t xml:space="preserve">2034-06-06</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -27041,40 +27041,40 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jørgens Alle 42</t>
+          <t xml:space="preserve">Gl. Randersvej 35</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t xml:space="preserve">8850</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t xml:space="preserve">7775696</t>
+          <t xml:space="preserve">8837678</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J361">
-        <v>394</v>
+        <v>13000</v>
       </c>
       <c r="K361" t="inlineStr">
         <is>
-          <t xml:space="preserve">311764588</t>
+          <t xml:space="preserve">311797218</t>
         </is>
       </c>
       <c r="L361" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ydes Bygningsrådgivning</t>
+          <t xml:space="preserve">Trykprøvning &amp; Energimærkning Danmark ApS</t>
         </is>
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-06-06</t>
+          <t xml:space="preserve">2034-11-13</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -27116,7 +27116,7 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl. Randersvej 35</t>
+          <t xml:space="preserve">Rughavevej 66</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
@@ -27126,30 +27126,30 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t xml:space="preserve">8837678</t>
+          <t xml:space="preserve">5590174</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="J362">
-        <v>13000</v>
+        <v>683</v>
       </c>
       <c r="K362" t="inlineStr">
         <is>
-          <t xml:space="preserve">311797218</t>
+          <t xml:space="preserve">311805525</t>
         </is>
       </c>
       <c r="L362" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trykprøvning &amp; Energimærkning Danmark ApS</t>
+          <t xml:space="preserve">Tæthedskompagniet ApS</t>
         </is>
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-11-13</t>
+          <t xml:space="preserve">2035-01-13</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -27191,7 +27191,7 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rughavevej 66</t>
+          <t xml:space="preserve">Sct. Leonis Gade 8</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
@@ -27201,30 +27201,30 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t xml:space="preserve">5590174</t>
+          <t xml:space="preserve">5585392</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J363">
-        <v>683</v>
+        <v>310</v>
       </c>
       <c r="K363" t="inlineStr">
         <is>
-          <t xml:space="preserve">311805525</t>
+          <t xml:space="preserve">311858724</t>
         </is>
       </c>
       <c r="L363" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tæthedskompagniet ApS</t>
+          <t xml:space="preserve">Norconsult Danmark A/S</t>
         </is>
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-01-13</t>
+          <t xml:space="preserve">2035-09-29</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -27266,17 +27266,17 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sct. Leonis Gade 8</t>
+          <t xml:space="preserve">Iglsøvej 68B</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">7850</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t xml:space="preserve">5585392</t>
+          <t xml:space="preserve">4048544</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -27285,21 +27285,21 @@
         </is>
       </c>
       <c r="J364">
-        <v>310</v>
+        <v>515</v>
       </c>
       <c r="K364" t="inlineStr">
         <is>
-          <t xml:space="preserve">311858724</t>
+          <t xml:space="preserve">311869171</t>
         </is>
       </c>
       <c r="L364" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norconsult Danmark A/S</t>
+          <t xml:space="preserve">Tæthedskompagniet ApS</t>
         </is>
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-29</t>
+          <t xml:space="preserve">2035-11-19</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -27326,12 +27326,12 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t xml:space="preserve">Viborg Kommune</t>
+          <t xml:space="preserve">Viborg Idrætshøjskole S/I</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -27341,40 +27341,40 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iglsøvej 68B</t>
+          <t xml:space="preserve">Vinkelvej 22A</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t xml:space="preserve">7850</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t xml:space="preserve">4048544</t>
+          <t xml:space="preserve">749139, 5594844</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="J365">
-        <v>515</v>
+        <v>348</v>
       </c>
       <c r="K365" t="inlineStr">
         <is>
-          <t xml:space="preserve">311869171</t>
+          <t xml:space="preserve">311879358</t>
         </is>
       </c>
       <c r="L365" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tæthedskompagniet ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-19</t>
+          <t xml:space="preserve">2036-01-29</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -27401,12 +27401,12 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t xml:space="preserve">Viborg Idrætshøjskole S/I</t>
+          <t xml:space="preserve">Viborg Kommune</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
@@ -27416,7 +27416,7 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vinkelvej 22A</t>
+          <t xml:space="preserve">Martinesminde 2</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
@@ -27426,30 +27426,30 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t xml:space="preserve">749139, 5594844</t>
+          <t xml:space="preserve">100617942</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J366">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K366" t="inlineStr">
         <is>
-          <t xml:space="preserve">311879358</t>
+          <t xml:space="preserve">311881722</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
         </is>
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-29</t>
+          <t xml:space="preserve">2036-02-12</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -27491,7 +27491,7 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martinesminde 2</t>
+          <t xml:space="preserve">Stænderpladsen 2</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
@@ -27501,30 +27501,30 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t xml:space="preserve">100617942</t>
+          <t xml:space="preserve">9431029</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J367">
-        <v>349</v>
+        <v>1500</v>
       </c>
       <c r="K367" t="inlineStr">
         <is>
-          <t xml:space="preserve">311881722</t>
+          <t xml:space="preserve">311929568</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-12</t>
+          <t xml:space="preserve">2036-10-02</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
